--- a/forecast_agent_output/sarimax_test.xlsx
+++ b/forecast_agent_output/sarimax_test.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80990.01489019298</v>
+        <v>72565.22108252623</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83117.65469372655</v>
+        <v>79594.12061332338</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79722.90935238518</v>
+        <v>76585.20784791537</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>98905.77898739433</v>
+        <v>97915.29396227446</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>117269.3110561718</v>
+        <v>116134.3733884495</v>
       </c>
       <c r="C6" t="n">
         <v>116395.8503</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>873.4607561717712</v>
+        <v>-261.4769115505333</v>
       </c>
       <c r="F6" t="n">
-        <v>873.4607561717712</v>
+        <v>261.4769115505333</v>
       </c>
     </row>
     <row r="7">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>228443.4881996023</v>
+        <v>225085.7034214892</v>
       </c>
       <c r="C7" t="n">
         <v>227764.6616</v>
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>678.8265996022965</v>
+        <v>-2678.958178510831</v>
       </c>
       <c r="F7" t="n">
-        <v>678.8265996022965</v>
+        <v>2678.958178510831</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>249875.2715037328</v>
+        <v>245623.4967936341</v>
       </c>
       <c r="C8" t="n">
         <v>248337.9203</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1537.351203732804</v>
+        <v>-2714.423506365885</v>
       </c>
       <c r="F8" t="n">
-        <v>1537.351203732804</v>
+        <v>2714.423506365885</v>
       </c>
     </row>
     <row r="9">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>164932.0372085319</v>
+        <v>165746.3530134213</v>
       </c>
       <c r="C9" t="n">
         <v>164272.0265</v>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>660.0107085319178</v>
+        <v>1474.326513421285</v>
       </c>
       <c r="F9" t="n">
-        <v>660.0107085319178</v>
+        <v>1474.326513421285</v>
       </c>
     </row>
     <row r="10">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141067.8472870304</v>
+        <v>131818.4586413392</v>
       </c>
       <c r="C10" t="n">
         <v>126885.9814</v>
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14181.86588703042</v>
+        <v>4932.477241339235</v>
       </c>
       <c r="F10" t="n">
-        <v>14181.86588703042</v>
+        <v>4932.477241339235</v>
       </c>
     </row>
   </sheetData>
